--- a/tagproject/results/annotations.xlsx
+++ b/tagproject/results/annotations.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C412"/>
+  <dimension ref="A1:C472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6610,6 +6610,906 @@
         </is>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>0</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Lorem</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>B-PER</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>0</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>ipsum</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>0</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>dolor</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>0</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>0</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>amet</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>0</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>consectetur</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>0</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>adipiscing</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>0</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>elit</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>1</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Sed</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>1</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>do</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>1</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>eiusmod</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>1</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>tempor</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>1</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>incididunt</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>1</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>1</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>labore</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>1</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>et</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>1</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>dolore</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>1</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>magna</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>1</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>aliqua</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>2</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Ut</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>2</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>enim</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>2</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>2</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>minim</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>2</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>veniam</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>2</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>quis</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>2</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>nostrud</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>2</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>exercitation</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>2</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>ullamco</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>2</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>laboris</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>2</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>nisi</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>2</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>2</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>aliquip</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>2</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>ex</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>2</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>2</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>commodo</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>2</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>consequat</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>3</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Duis</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>3</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>aute</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>3</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>irure</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>3</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>dolor</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>3</v>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>3</v>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>reprehenderit</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>3</v>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>voluptate</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>3</v>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>velit</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>3</v>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>esse</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>3</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>cillum</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>3</v>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>dolore</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>3</v>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>3</v>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>fugiat</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>3</v>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>nulla</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>3</v>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>pariatur</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>4</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Excepteur</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>4</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>sint</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>4</v>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>occaecat</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>4</v>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>cupidatat</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>4</v>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>4</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>proident</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>4</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>sunt</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>4</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>4</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>culpa</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
